--- a/Advanced_Military_Risk_AnalysisT.xlsx
+++ b/Advanced_Military_Risk_AnalysisT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBFB8ACC-C620-4DFA-BCAA-E49DFF092722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDF6787-8063-4C23-8D99-31DBF910D321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D8971F51-45C4-4DE5-BE2B-916AE27C21DD}"/>
   </bookViews>
@@ -25,12 +25,6 @@
     <t>Unit ID Code</t>
   </si>
   <si>
-    <t>Active Combat Unit Name</t>
-  </si>
-  <si>
-    <t>Strategic Command Sector</t>
-  </si>
-  <si>
     <t>Allocated Equipment</t>
   </si>
   <si>
@@ -260,6 +254,12 @@
   </si>
   <si>
     <t>OPTIMAL - MISSION READY</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Agency</t>
   </si>
 </sst>
 </file>
@@ -924,18 +924,6 @@
   </cellStyles>
   <dxfs count="12">
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1086,6 +1074,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -1093,18 +1090,21 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -1121,17 +1121,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B48DD247-315D-4B30-9FC3-1A5665554389}" name="Table1" displayName="Table1" ref="A1:H26" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B48DD247-315D-4B30-9FC3-1A5665554389}" name="Table1" displayName="Table1" ref="A1:H26" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="A1:H26" xr:uid="{B48DD247-315D-4B30-9FC3-1A5665554389}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D083A4F2-E5E9-45EC-AB62-5AB45E7050F9}" name="Unit ID Code" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{DBEB83D9-9BBF-4230-B804-8D362301DA65}" name="Active Combat Unit Name" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{682DC804-AF85-40F0-92C7-C07B2E577B9D}" name="Strategic Command Sector" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{EF530436-B672-4ACB-B6D8-1D1435EEC865}" name="Allocated Equipment" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{C5DFB553-D5DB-4E79-AEAF-8FBD8F281A02}" name="Bulk Item Inventory Count" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{FC28E2E4-18A8-4965-8DCE-CA9B706DB250}" name="Lifetime Maintenance Run Hours" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{BED8D32D-1A36-4283-B4CD-12DEAEEF65D2}" name="Utilization Intensity Ratio" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{E9BF35D4-E09E-4B55-ADA6-819BCC21F3A7}" name="Maintenance Risk Index (MRI)" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{D083A4F2-E5E9-45EC-AB62-5AB45E7050F9}" name="Unit ID Code" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{DBEB83D9-9BBF-4230-B804-8D362301DA65}" name="Agency" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{682DC804-AF85-40F0-92C7-C07B2E577B9D}" name="Region" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{EF530436-B672-4ACB-B6D8-1D1435EEC865}" name="Allocated Equipment" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{C5DFB553-D5DB-4E79-AEAF-8FBD8F281A02}" name="Bulk Item Inventory Count" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{FC28E2E4-18A8-4965-8DCE-CA9B706DB250}" name="Lifetime Maintenance Run Hours" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{BED8D32D-1A36-4283-B4CD-12DEAEEF65D2}" name="Utilization Intensity Ratio" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{E9BF35D4-E09E-4B55-ADA6-819BCC21F3A7}" name="Maintenance Risk Index (MRI)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1472,40 +1472,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>7</v>
       </c>
       <c r="W1" s="4"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="E2" s="1">
         <v>85</v>
@@ -1517,22 +1517,22 @@
         <v>107.07</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="W2" s="4"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="E3" s="1">
         <v>120</v>
@@ -1544,22 +1544,22 @@
         <v>46.67</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="W3" s="4"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="E4" s="1">
         <v>240</v>
@@ -1571,22 +1571,22 @@
         <v>20</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="W4" s="4"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E5" s="1">
         <v>310</v>
@@ -1598,22 +1598,22 @@
         <v>12.74</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="W5" s="4"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="E6" s="1">
         <v>680</v>
@@ -1625,22 +1625,22 @@
         <v>1.31</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W6" s="4"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="E7" s="1">
         <v>1400</v>
@@ -1652,22 +1652,22 @@
         <v>1.07</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W7" s="4"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="E8" s="1">
         <v>1200</v>
@@ -1679,22 +1679,22 @@
         <v>0.95</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W8" s="4"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="E9" s="1">
         <v>1500</v>
@@ -1706,22 +1706,22 @@
         <v>0.89</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W9" s="4"/>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="E10" s="1">
         <v>3800</v>
@@ -1733,22 +1733,22 @@
         <v>0.63</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W10" s="4"/>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="E11" s="1">
         <v>3100</v>
@@ -1760,22 +1760,22 @@
         <v>0.6</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W11" s="4"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="E12" s="1">
         <v>3900</v>
@@ -1787,22 +1787,22 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W12" s="4"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="E13" s="1">
         <v>3400</v>
@@ -1814,22 +1814,22 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W13" s="4"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E14" s="1">
         <v>5800</v>
@@ -1841,22 +1841,22 @@
         <v>0.51</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W14" s="4"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="C15" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E15" s="1">
         <v>6200</v>
@@ -1868,22 +1868,22 @@
         <v>0.5</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W15" s="4"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E16" s="1">
         <v>1920</v>
@@ -1895,22 +1895,22 @@
         <v>0.44</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W16" s="4"/>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="E17" s="1">
         <v>950</v>
@@ -1922,22 +1922,22 @@
         <v>0.43</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W17" s="4"/>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="E18" s="1">
         <v>3200</v>
@@ -1949,22 +1949,22 @@
         <v>0.4</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W18" s="4"/>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E19" s="1">
         <v>1850</v>
@@ -1976,22 +1976,22 @@
         <v>0.39</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W19" s="4"/>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E20" s="1">
         <v>5100</v>
@@ -2003,22 +2003,22 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W20" s="4"/>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E21" s="1">
         <v>4950</v>
@@ -2030,22 +2030,22 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W21" s="4"/>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="E22" s="1">
         <v>4500</v>
@@ -2057,22 +2057,22 @@
         <v>0.27</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W22" s="4"/>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E23" s="1">
         <v>4200</v>
@@ -2084,22 +2084,22 @@
         <v>0.27</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W23" s="4"/>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="E24" s="1">
         <v>4120</v>
@@ -2111,22 +2111,22 @@
         <v>0.24</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W24" s="4"/>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="C25" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E25" s="1">
         <v>4300</v>
@@ -2138,22 +2138,22 @@
         <v>0.24</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W25" s="4"/>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E26" s="10">
         <v>2800</v>
@@ -2165,7 +2165,7 @@
         <v>0.23</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W26" s="5"/>
     </row>
